--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4273"/>
+  <dimension ref="A1:F4274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85744,7 +85744,7 @@
         <v>79091.97</v>
       </c>
       <c r="F4266" t="n">
-        <v>3298.65347113</v>
+        <v>3294.10382328</v>
       </c>
     </row>
     <row r="4267">
@@ -85764,7 +85764,7 @@
         <v>78447.11</v>
       </c>
       <c r="F4267" t="n">
-        <v>5167.76242688</v>
+        <v>5154.03450645</v>
       </c>
     </row>
     <row r="4268">
@@ -85784,7 +85784,7 @@
         <v>78283.98</v>
       </c>
       <c r="F4268" t="n">
-        <v>5261.48905322</v>
+        <v>5259.48606005</v>
       </c>
     </row>
     <row r="4269">
@@ -85804,7 +85804,7 @@
         <v>76536.55</v>
       </c>
       <c r="F4269" t="n">
-        <v>6398.15202397</v>
+        <v>6391.37950291</v>
       </c>
     </row>
     <row r="4270">
@@ -85864,7 +85864,7 @@
         <v>76799.85000000001</v>
       </c>
       <c r="F4272" t="n">
-        <v>2226.48727095</v>
+        <v>2218.66675599</v>
       </c>
     </row>
     <row r="4273">
@@ -85881,10 +85881,30 @@
         <v>76347.27</v>
       </c>
       <c r="E4273" t="n">
-        <v>78590.72</v>
+        <v>78175.00999999999</v>
       </c>
       <c r="F4273" t="n">
-        <v>6249.93566287</v>
+        <v>6593.9641279</v>
+      </c>
+    </row>
+    <row r="4274">
+      <c r="A4274" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B4274" t="n">
+        <v>78175</v>
+      </c>
+      <c r="C4274" t="n">
+        <v>78242.75999999999</v>
+      </c>
+      <c r="D4274" t="n">
+        <v>74887.5</v>
+      </c>
+      <c r="E4274" t="n">
+        <v>75173.00999999999</v>
+      </c>
+      <c r="F4274" t="n">
+        <v>9700.3727899</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4274"/>
+  <dimension ref="A1:F4275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85744,7 +85744,7 @@
         <v>79091.97</v>
       </c>
       <c r="F4266" t="n">
-        <v>3294.10382328</v>
+        <v>3298.65347113</v>
       </c>
     </row>
     <row r="4267">
@@ -85764,7 +85764,7 @@
         <v>78447.11</v>
       </c>
       <c r="F4267" t="n">
-        <v>5154.03450645</v>
+        <v>5167.76242688</v>
       </c>
     </row>
     <row r="4268">
@@ -85784,7 +85784,7 @@
         <v>78283.98</v>
       </c>
       <c r="F4268" t="n">
-        <v>5259.48606005</v>
+        <v>5261.48905322</v>
       </c>
     </row>
     <row r="4269">
@@ -85804,7 +85804,7 @@
         <v>76536.55</v>
       </c>
       <c r="F4269" t="n">
-        <v>6391.37950291</v>
+        <v>6398.15202397</v>
       </c>
     </row>
     <row r="4270">
@@ -85901,10 +85901,30 @@
         <v>74887.5</v>
       </c>
       <c r="E4274" t="n">
-        <v>75173.00999999999</v>
+        <v>75584.17</v>
       </c>
       <c r="F4274" t="n">
-        <v>9700.3727899</v>
+        <v>10173.51613169</v>
+      </c>
+    </row>
+    <row r="4275">
+      <c r="A4275" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B4275" t="n">
+        <v>75584.17</v>
+      </c>
+      <c r="C4275" t="n">
+        <v>76499.99000000001</v>
+      </c>
+      <c r="D4275" t="n">
+        <v>74911.53</v>
+      </c>
+      <c r="E4275" t="n">
+        <v>75624.32000000001</v>
+      </c>
+      <c r="F4275" t="n">
+        <v>6721.57729647</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4275"/>
+  <dimension ref="A1:F4276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85744,7 +85744,7 @@
         <v>79091.97</v>
       </c>
       <c r="F4266" t="n">
-        <v>3298.65347113</v>
+        <v>3294.10382328</v>
       </c>
     </row>
     <row r="4267">
@@ -85764,7 +85764,7 @@
         <v>78447.11</v>
       </c>
       <c r="F4267" t="n">
-        <v>5167.76242688</v>
+        <v>5154.03450645</v>
       </c>
     </row>
     <row r="4268">
@@ -85784,7 +85784,7 @@
         <v>78283.98</v>
       </c>
       <c r="F4268" t="n">
-        <v>5261.48905322</v>
+        <v>5259.48606005</v>
       </c>
     </row>
     <row r="4269">
@@ -85804,7 +85804,7 @@
         <v>76536.55</v>
       </c>
       <c r="F4269" t="n">
-        <v>6398.15202397</v>
+        <v>6391.37950291</v>
       </c>
     </row>
     <row r="4270">
@@ -85904,7 +85904,7 @@
         <v>75584.17</v>
       </c>
       <c r="F4274" t="n">
-        <v>10173.51613169</v>
+        <v>10162.32298722</v>
       </c>
     </row>
     <row r="4275">
@@ -85921,10 +85921,30 @@
         <v>74911.53</v>
       </c>
       <c r="E4275" t="n">
-        <v>75624.32000000001</v>
+        <v>76144.99000000001</v>
       </c>
       <c r="F4275" t="n">
-        <v>6721.57729647</v>
+        <v>6970.77840696</v>
+      </c>
+    </row>
+    <row r="4276">
+      <c r="A4276" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B4276" t="n">
+        <v>76144.99000000001</v>
+      </c>
+      <c r="C4276" t="n">
+        <v>77105.42</v>
+      </c>
+      <c r="D4276" t="n">
+        <v>75921.88</v>
+      </c>
+      <c r="E4276" t="n">
+        <v>76207.05</v>
+      </c>
+      <c r="F4276" t="n">
+        <v>5135.80771264</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4276"/>
+  <dimension ref="A1:F4277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85744,7 +85744,7 @@
         <v>79091.97</v>
       </c>
       <c r="F4266" t="n">
-        <v>3294.10382328</v>
+        <v>3298.65347113</v>
       </c>
     </row>
     <row r="4267">
@@ -85764,7 +85764,7 @@
         <v>78447.11</v>
       </c>
       <c r="F4267" t="n">
-        <v>5154.03450645</v>
+        <v>5167.76242688</v>
       </c>
     </row>
     <row r="4268">
@@ -85784,7 +85784,7 @@
         <v>78283.98</v>
       </c>
       <c r="F4268" t="n">
-        <v>5259.48606005</v>
+        <v>5261.48905322</v>
       </c>
     </row>
     <row r="4269">
@@ -85804,7 +85804,7 @@
         <v>76536.55</v>
       </c>
       <c r="F4269" t="n">
-        <v>6391.37950291</v>
+        <v>6398.15202397</v>
       </c>
     </row>
     <row r="4270">
@@ -85924,7 +85924,7 @@
         <v>76144.99000000001</v>
       </c>
       <c r="F4275" t="n">
-        <v>6970.77840696</v>
+        <v>6956.58620231</v>
       </c>
     </row>
     <row r="4276">
@@ -85941,10 +85941,30 @@
         <v>75921.88</v>
       </c>
       <c r="E4276" t="n">
-        <v>76207.05</v>
+        <v>76348.74000000001</v>
       </c>
       <c r="F4276" t="n">
-        <v>5135.80771264</v>
+        <v>5368.21439806</v>
+      </c>
+    </row>
+    <row r="4277">
+      <c r="A4277" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B4277" t="n">
+        <v>76348.74000000001</v>
+      </c>
+      <c r="C4277" t="n">
+        <v>81388.47</v>
+      </c>
+      <c r="D4277" t="n">
+        <v>76205.46000000001</v>
+      </c>
+      <c r="E4277" t="n">
+        <v>81310.67</v>
+      </c>
+      <c r="F4277" t="n">
+        <v>12075.77170343</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4277"/>
+  <dimension ref="A1:F4280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85744,7 +85744,7 @@
         <v>79091.97</v>
       </c>
       <c r="F4266" t="n">
-        <v>3298.65347113</v>
+        <v>3294.10382328</v>
       </c>
     </row>
     <row r="4267">
@@ -85764,7 +85764,7 @@
         <v>78447.11</v>
       </c>
       <c r="F4267" t="n">
-        <v>5167.76242688</v>
+        <v>5154.03450645</v>
       </c>
     </row>
     <row r="4268">
@@ -85784,7 +85784,7 @@
         <v>78283.98</v>
       </c>
       <c r="F4268" t="n">
-        <v>5261.48905322</v>
+        <v>5259.48606005</v>
       </c>
     </row>
     <row r="4269">
@@ -85804,7 +85804,7 @@
         <v>76536.55</v>
       </c>
       <c r="F4269" t="n">
-        <v>6398.15202397</v>
+        <v>6391.37950291</v>
       </c>
     </row>
     <row r="4270">
@@ -85884,7 +85884,7 @@
         <v>78175.00999999999</v>
       </c>
       <c r="F4273" t="n">
-        <v>6593.9641279</v>
+        <v>6579.59428717</v>
       </c>
     </row>
     <row r="4274">
@@ -85961,10 +85961,70 @@
         <v>76205.46000000001</v>
       </c>
       <c r="E4277" t="n">
-        <v>81310.67</v>
+        <v>80875.03999999999</v>
       </c>
       <c r="F4277" t="n">
-        <v>12075.77170343</v>
+        <v>12369.95504853</v>
+      </c>
+    </row>
+    <row r="4278">
+      <c r="A4278" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B4278" t="n">
+        <v>80875.03999999999</v>
+      </c>
+      <c r="C4278" t="n">
+        <v>81925</v>
+      </c>
+      <c r="D4278" t="n">
+        <v>80822.48</v>
+      </c>
+      <c r="E4278" t="n">
+        <v>81233.91</v>
+      </c>
+      <c r="F4278" t="n">
+        <v>3325.31440002</v>
+      </c>
+    </row>
+    <row r="4279">
+      <c r="A4279" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B4279" t="n">
+        <v>81233.91</v>
+      </c>
+      <c r="C4279" t="n">
+        <v>81472.03999999999</v>
+      </c>
+      <c r="D4279" t="n">
+        <v>80085</v>
+      </c>
+      <c r="E4279" t="n">
+        <v>81159.64</v>
+      </c>
+      <c r="F4279" t="n">
+        <v>3613.32299631</v>
+      </c>
+    </row>
+    <row r="4280">
+      <c r="A4280" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B4280" t="n">
+        <v>81160.33</v>
+      </c>
+      <c r="C4280" t="n">
+        <v>87397</v>
+      </c>
+      <c r="D4280" t="n">
+        <v>80837.42</v>
+      </c>
+      <c r="E4280" t="n">
+        <v>86561.87</v>
+      </c>
+      <c r="F4280" t="n">
+        <v>13520.25973626</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4282"/>
+  <dimension ref="A1:F4283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86044,7 +86044,7 @@
         <v>86198.05</v>
       </c>
       <c r="F4281" t="n">
-        <v>8944.378048070001</v>
+        <v>8943.875888770001</v>
       </c>
     </row>
     <row r="4282">
@@ -86061,10 +86061,30 @@
         <v>83513</v>
       </c>
       <c r="E4282" t="n">
-        <v>84517.60000000001</v>
+        <v>84378.31</v>
       </c>
       <c r="F4282" t="n">
-        <v>7618.32206263</v>
+        <v>7856.10631934</v>
+      </c>
+    </row>
+    <row r="4283">
+      <c r="A4283" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B4283" t="n">
+        <v>84378.31</v>
+      </c>
+      <c r="C4283" t="n">
+        <v>84929.78</v>
+      </c>
+      <c r="D4283" t="n">
+        <v>82708.96000000001</v>
+      </c>
+      <c r="E4283" t="n">
+        <v>84060.3</v>
+      </c>
+      <c r="F4283" t="n">
+        <v>6654.96748484</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4284"/>
+  <dimension ref="A1:F4287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86084,7 +86084,7 @@
         <v>84385.46000000001</v>
       </c>
       <c r="F4283" t="n">
-        <v>6840.72162128</v>
+        <v>6839.85476141</v>
       </c>
     </row>
     <row r="4284">
@@ -86101,10 +86101,70 @@
         <v>83091.19</v>
       </c>
       <c r="E4284" t="n">
-        <v>83948.02</v>
+        <v>84093.13</v>
       </c>
       <c r="F4284" t="n">
-        <v>7103.10172737</v>
+        <v>7278.050955</v>
+      </c>
+    </row>
+    <row r="4285">
+      <c r="A4285" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B4285" t="n">
+        <v>84093.13</v>
+      </c>
+      <c r="C4285" t="n">
+        <v>84470.44</v>
+      </c>
+      <c r="D4285" t="n">
+        <v>83777.77</v>
+      </c>
+      <c r="E4285" t="n">
+        <v>84416.64999999999</v>
+      </c>
+      <c r="F4285" t="n">
+        <v>1999.02703222</v>
+      </c>
+    </row>
+    <row r="4286">
+      <c r="A4286" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B4286" t="n">
+        <v>84416.64</v>
+      </c>
+      <c r="C4286" t="n">
+        <v>85158.5</v>
+      </c>
+      <c r="D4286" t="n">
+        <v>84113.56</v>
+      </c>
+      <c r="E4286" t="n">
+        <v>84462.14</v>
+      </c>
+      <c r="F4286" t="n">
+        <v>2958.07329191</v>
+      </c>
+    </row>
+    <row r="4287">
+      <c r="A4287" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B4287" t="n">
+        <v>84463.08</v>
+      </c>
+      <c r="C4287" t="n">
+        <v>84992</v>
+      </c>
+      <c r="D4287" t="n">
+        <v>82510.37</v>
+      </c>
+      <c r="E4287" t="n">
+        <v>83169.32000000001</v>
+      </c>
+      <c r="F4287" t="n">
+        <v>6534.94859463</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4287"/>
+  <dimension ref="A1:F4288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86024,7 +86024,7 @@
         <v>86594.94</v>
       </c>
       <c r="F4280" t="n">
-        <v>14122.3475358</v>
+        <v>14086.87276351</v>
       </c>
     </row>
     <row r="4281">
@@ -86144,7 +86144,7 @@
         <v>84462.14</v>
       </c>
       <c r="F4286" t="n">
-        <v>2958.07329191</v>
+        <v>2958.05456342</v>
       </c>
     </row>
     <row r="4287">
@@ -86161,10 +86161,30 @@
         <v>82510.37</v>
       </c>
       <c r="E4287" t="n">
-        <v>83169.32000000001</v>
+        <v>83456.74000000001</v>
       </c>
       <c r="F4287" t="n">
-        <v>6534.94859463</v>
+        <v>6691.59471669</v>
+      </c>
+    </row>
+    <row r="4288">
+      <c r="A4288" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B4288" t="n">
+        <v>83456.74000000001</v>
+      </c>
+      <c r="C4288" t="n">
+        <v>84557.00999999999</v>
+      </c>
+      <c r="D4288" t="n">
+        <v>82736</v>
+      </c>
+      <c r="E4288" t="n">
+        <v>83612.14</v>
+      </c>
+      <c r="F4288" t="n">
+        <v>4837.43778434</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4288"/>
+  <dimension ref="A1:F4289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86024,7 +86024,7 @@
         <v>86594.94</v>
       </c>
       <c r="F4280" t="n">
-        <v>14086.87276351</v>
+        <v>14122.3475358</v>
       </c>
     </row>
     <row r="4281">
@@ -86164,7 +86164,7 @@
         <v>83456.74000000001</v>
       </c>
       <c r="F4287" t="n">
-        <v>6691.59471669</v>
+        <v>6680.32502949</v>
       </c>
     </row>
     <row r="4288">
@@ -86181,10 +86181,30 @@
         <v>82736</v>
       </c>
       <c r="E4288" t="n">
-        <v>83612.14</v>
+        <v>83638.42</v>
       </c>
       <c r="F4288" t="n">
-        <v>4837.43778434</v>
+        <v>4988.49271838</v>
+      </c>
+    </row>
+    <row r="4289">
+      <c r="A4289" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B4289" t="n">
+        <v>83638.42</v>
+      </c>
+      <c r="C4289" t="n">
+        <v>85613.72</v>
+      </c>
+      <c r="D4289" t="n">
+        <v>82911.86</v>
+      </c>
+      <c r="E4289" t="n">
+        <v>83706.13</v>
+      </c>
+      <c r="F4289" t="n">
+        <v>6759.76971891</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4289"/>
+  <dimension ref="A1:F4290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86184,7 +86184,7 @@
         <v>83638.42</v>
       </c>
       <c r="F4288" t="n">
-        <v>4988.49271838</v>
+        <v>4988.45039973</v>
       </c>
     </row>
     <row r="4289">
@@ -86201,10 +86201,30 @@
         <v>82911.86</v>
       </c>
       <c r="E4289" t="n">
-        <v>83706.13</v>
+        <v>83556.14</v>
       </c>
       <c r="F4289" t="n">
-        <v>6759.76971891</v>
+        <v>7056.49784774</v>
+      </c>
+    </row>
+    <row r="4290">
+      <c r="A4290" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B4290" t="n">
+        <v>83556.14</v>
+      </c>
+      <c r="C4290" t="n">
+        <v>85244</v>
+      </c>
+      <c r="D4290" t="n">
+        <v>83107.03</v>
+      </c>
+      <c r="E4290" t="n">
+        <v>84728.07000000001</v>
+      </c>
+      <c r="F4290" t="n">
+        <v>6522.43495656</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4290"/>
+  <dimension ref="A1:F4291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86004,7 +86004,7 @@
         <v>81159.64</v>
       </c>
       <c r="F4279" t="n">
-        <v>3613.32299631</v>
+        <v>3612.2748174</v>
       </c>
     </row>
     <row r="4280">
@@ -86024,7 +86024,7 @@
         <v>86594.94</v>
       </c>
       <c r="F4280" t="n">
-        <v>14122.3475358</v>
+        <v>14086.87276351</v>
       </c>
     </row>
     <row r="4281">
@@ -86064,7 +86064,7 @@
         <v>84378.31</v>
       </c>
       <c r="F4282" t="n">
-        <v>7856.10631934</v>
+        <v>7859.85987871</v>
       </c>
     </row>
     <row r="4283">
@@ -86124,7 +86124,7 @@
         <v>84416.64999999999</v>
       </c>
       <c r="F4285" t="n">
-        <v>1999.02703222</v>
+        <v>1990.68250788</v>
       </c>
     </row>
     <row r="4286">
@@ -86184,7 +86184,7 @@
         <v>83638.42</v>
       </c>
       <c r="F4288" t="n">
-        <v>4988.45039973</v>
+        <v>4975.88497273</v>
       </c>
     </row>
     <row r="4289">
@@ -86204,7 +86204,7 @@
         <v>83556.14</v>
       </c>
       <c r="F4289" t="n">
-        <v>7056.49784774</v>
+        <v>7050.62207426</v>
       </c>
     </row>
     <row r="4290">
@@ -86221,10 +86221,30 @@
         <v>83107.03</v>
       </c>
       <c r="E4290" t="n">
-        <v>84728.07000000001</v>
+        <v>84848.73</v>
       </c>
       <c r="F4290" t="n">
-        <v>6522.43495656</v>
+        <v>6624.10536633</v>
+      </c>
+    </row>
+    <row r="4291">
+      <c r="A4291" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B4291" t="n">
+        <v>84848.73</v>
+      </c>
+      <c r="C4291" t="n">
+        <v>87249.05</v>
+      </c>
+      <c r="D4291" t="n">
+        <v>83850.02</v>
+      </c>
+      <c r="E4291" t="n">
+        <v>84529</v>
+      </c>
+      <c r="F4291" t="n">
+        <v>8640.575284910001</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4294"/>
+  <dimension ref="A1:F4295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86184,7 +86184,7 @@
         <v>83638.42</v>
       </c>
       <c r="F4288" t="n">
-        <v>4975.88497273</v>
+        <v>4988.45039973</v>
       </c>
     </row>
     <row r="4289">
@@ -86301,10 +86301,30 @@
         <v>84944.2</v>
       </c>
       <c r="E4294" t="n">
-        <v>85930.16</v>
+        <v>85748.96000000001</v>
       </c>
       <c r="F4294" t="n">
-        <v>5099.03610811</v>
+        <v>5361.8875615</v>
+      </c>
+    </row>
+    <row r="4295">
+      <c r="A4295" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B4295" t="n">
+        <v>85748.96000000001</v>
+      </c>
+      <c r="C4295" t="n">
+        <v>86698.35000000001</v>
+      </c>
+      <c r="D4295" t="n">
+        <v>85100.00999999999</v>
+      </c>
+      <c r="E4295" t="n">
+        <v>85543.28</v>
+      </c>
+      <c r="F4295" t="n">
+        <v>4570.05465747</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4297"/>
+  <dimension ref="A1:F4298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86184,7 +86184,7 @@
         <v>83638.42</v>
       </c>
       <c r="F4288" t="n">
-        <v>4975.88497273</v>
+        <v>4988.45039973</v>
       </c>
     </row>
     <row r="4289">
@@ -86244,7 +86244,7 @@
         <v>84504.88</v>
       </c>
       <c r="F4291" t="n">
-        <v>8764.833729800001</v>
+        <v>8771.11595673</v>
       </c>
     </row>
     <row r="4292">
@@ -86264,7 +86264,7 @@
         <v>84742.22</v>
       </c>
       <c r="F4292" t="n">
-        <v>1922.47843764</v>
+        <v>1924.17767592</v>
       </c>
     </row>
     <row r="4293">
@@ -86304,7 +86304,7 @@
         <v>85748.96000000001</v>
       </c>
       <c r="F4294" t="n">
-        <v>5356.80532961</v>
+        <v>5361.8875615</v>
       </c>
     </row>
     <row r="4295">
@@ -86324,7 +86324,7 @@
         <v>85539.77</v>
       </c>
       <c r="F4295" t="n">
-        <v>4709.03201583</v>
+        <v>4736.67950708</v>
       </c>
     </row>
     <row r="4296">
@@ -86361,10 +86361,30 @@
         <v>80314.7</v>
       </c>
       <c r="E4297" t="n">
-        <v>81711.5</v>
+        <v>81692.78999999999</v>
       </c>
       <c r="F4297" t="n">
-        <v>8450.2442467</v>
+        <v>8624.88509828</v>
+      </c>
+    </row>
+    <row r="4298">
+      <c r="A4298" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B4298" t="n">
+        <v>81692.78999999999</v>
+      </c>
+      <c r="C4298" t="n">
+        <v>83452.99000000001</v>
+      </c>
+      <c r="D4298" t="n">
+        <v>81534.02</v>
+      </c>
+      <c r="E4298" t="n">
+        <v>82464.72</v>
+      </c>
+      <c r="F4298" t="n">
+        <v>4282.97166963</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4298"/>
+  <dimension ref="A1:F4301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86184,7 +86184,7 @@
         <v>83638.42</v>
       </c>
       <c r="F4288" t="n">
-        <v>4988.45039973</v>
+        <v>4975.88497273</v>
       </c>
     </row>
     <row r="4289">
@@ -86244,7 +86244,7 @@
         <v>84504.88</v>
       </c>
       <c r="F4291" t="n">
-        <v>8771.11595673</v>
+        <v>8764.833729800001</v>
       </c>
     </row>
     <row r="4292">
@@ -86264,7 +86264,7 @@
         <v>84742.22</v>
       </c>
       <c r="F4292" t="n">
-        <v>1924.17767592</v>
+        <v>1922.47843764</v>
       </c>
     </row>
     <row r="4293">
@@ -86304,7 +86304,7 @@
         <v>85748.96000000001</v>
       </c>
       <c r="F4294" t="n">
-        <v>5361.8875615</v>
+        <v>5356.80532961</v>
       </c>
     </row>
     <row r="4295">
@@ -86324,7 +86324,7 @@
         <v>85539.77</v>
       </c>
       <c r="F4295" t="n">
-        <v>4736.67950708</v>
+        <v>4709.03201583</v>
       </c>
     </row>
     <row r="4296">
@@ -86364,7 +86364,7 @@
         <v>81692.78999999999</v>
       </c>
       <c r="F4297" t="n">
-        <v>8624.88509828</v>
+        <v>8619.62292052</v>
       </c>
     </row>
     <row r="4298">
@@ -86381,10 +86381,70 @@
         <v>81534.02</v>
       </c>
       <c r="E4298" t="n">
-        <v>82464.72</v>
+        <v>82544.71000000001</v>
       </c>
       <c r="F4298" t="n">
-        <v>4282.97166963</v>
+        <v>4468.26430575</v>
+      </c>
+    </row>
+    <row r="4299">
+      <c r="A4299" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B4299" t="n">
+        <v>82544.71000000001</v>
+      </c>
+      <c r="C4299" t="n">
+        <v>83093.39</v>
+      </c>
+      <c r="D4299" t="n">
+        <v>82458.02</v>
+      </c>
+      <c r="E4299" t="n">
+        <v>82910.8</v>
+      </c>
+      <c r="F4299" t="n">
+        <v>1623.3813987</v>
+      </c>
+    </row>
+    <row r="4300">
+      <c r="A4300" s="1" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B4300" t="n">
+        <v>82910.8</v>
+      </c>
+      <c r="C4300" t="n">
+        <v>84110.99000000001</v>
+      </c>
+      <c r="D4300" t="n">
+        <v>82714.25</v>
+      </c>
+      <c r="E4300" t="n">
+        <v>83678.28999999999</v>
+      </c>
+      <c r="F4300" t="n">
+        <v>2134.75734305</v>
+      </c>
+    </row>
+    <row r="4301">
+      <c r="A4301" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B4301" t="n">
+        <v>83678.28999999999</v>
+      </c>
+      <c r="C4301" t="n">
+        <v>84261.99000000001</v>
+      </c>
+      <c r="D4301" t="n">
+        <v>82199.25999999999</v>
+      </c>
+      <c r="E4301" t="n">
+        <v>82515.03</v>
+      </c>
+      <c r="F4301" t="n">
+        <v>4196.97073612</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4301"/>
+  <dimension ref="A1:F4302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86438,13 +86438,33 @@
         <v>84261.99000000001</v>
       </c>
       <c r="D4301" t="n">
-        <v>82199.25999999999</v>
+        <v>81634.08</v>
       </c>
       <c r="E4301" t="n">
-        <v>82515.03</v>
+        <v>81742.5</v>
       </c>
       <c r="F4301" t="n">
-        <v>4196.97073612</v>
+        <v>4736.09895644</v>
+      </c>
+    </row>
+    <row r="4302">
+      <c r="A4302" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B4302" t="n">
+        <v>81735.60000000001</v>
+      </c>
+      <c r="C4302" t="n">
+        <v>84070.33</v>
+      </c>
+      <c r="D4302" t="n">
+        <v>80927.48</v>
+      </c>
+      <c r="E4302" t="n">
+        <v>83363.14</v>
+      </c>
+      <c r="F4302" t="n">
+        <v>4906.08863301</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4302"/>
+  <dimension ref="A1:F4303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86404,7 +86404,7 @@
         <v>82910.8</v>
       </c>
       <c r="F4299" t="n">
-        <v>1623.3813987</v>
+        <v>1617.0954609</v>
       </c>
     </row>
     <row r="4300">
@@ -86424,7 +86424,7 @@
         <v>83678.28999999999</v>
       </c>
       <c r="F4300" t="n">
-        <v>2134.75734305</v>
+        <v>2131.89725576</v>
       </c>
     </row>
     <row r="4301">
@@ -86444,7 +86444,7 @@
         <v>81742.5</v>
       </c>
       <c r="F4301" t="n">
-        <v>4736.09895644</v>
+        <v>4727.51073414</v>
       </c>
     </row>
     <row r="4302">
@@ -86461,10 +86461,30 @@
         <v>80927.48</v>
       </c>
       <c r="E4302" t="n">
-        <v>83363.14</v>
+        <v>83101.99000000001</v>
       </c>
       <c r="F4302" t="n">
-        <v>4906.08863301</v>
+        <v>5189.37640199</v>
+      </c>
+    </row>
+    <row r="4303">
+      <c r="A4303" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B4303" t="n">
+        <v>83101.99000000001</v>
+      </c>
+      <c r="C4303" t="n">
+        <v>84062.11</v>
+      </c>
+      <c r="D4303" t="n">
+        <v>81400.00999999999</v>
+      </c>
+      <c r="E4303" t="n">
+        <v>81470.36</v>
+      </c>
+      <c r="F4303" t="n">
+        <v>6301.56495915</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4303"/>
+  <dimension ref="A1:F4304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86478,13 +86478,33 @@
         <v>84062.11</v>
       </c>
       <c r="D4303" t="n">
-        <v>81400.00999999999</v>
+        <v>81332.14999999999</v>
       </c>
       <c r="E4303" t="n">
-        <v>81470.36</v>
+        <v>81566.28999999999</v>
       </c>
       <c r="F4303" t="n">
-        <v>6301.56495915</v>
+        <v>6537.00204256</v>
+      </c>
+    </row>
+    <row r="4304">
+      <c r="A4304" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B4304" t="n">
+        <v>81566.28</v>
+      </c>
+      <c r="C4304" t="n">
+        <v>82555.08</v>
+      </c>
+      <c r="D4304" t="n">
+        <v>79676.02</v>
+      </c>
+      <c r="E4304" t="n">
+        <v>82486.85000000001</v>
+      </c>
+      <c r="F4304" t="n">
+        <v>6943.36449526</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4304"/>
+  <dimension ref="A1:F4305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86484,7 +86484,7 @@
         <v>81566.28999999999</v>
       </c>
       <c r="F4303" t="n">
-        <v>6537.00204256</v>
+        <v>6528.31956339</v>
       </c>
     </row>
     <row r="4304">
@@ -86501,10 +86501,30 @@
         <v>79676.02</v>
       </c>
       <c r="E4304" t="n">
-        <v>82486.85000000001</v>
+        <v>82131.46000000001</v>
       </c>
       <c r="F4304" t="n">
-        <v>6943.36449526</v>
+        <v>7100.55010209</v>
+      </c>
+    </row>
+    <row r="4305">
+      <c r="A4305" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B4305" t="n">
+        <v>82131.46000000001</v>
+      </c>
+      <c r="C4305" t="n">
+        <v>82831.00999999999</v>
+      </c>
+      <c r="D4305" t="n">
+        <v>80693.69</v>
+      </c>
+      <c r="E4305" t="n">
+        <v>81666.92</v>
+      </c>
+      <c r="F4305" t="n">
+        <v>4980.69655974</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4305"/>
+  <dimension ref="A1:F4308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86464,7 +86464,7 @@
         <v>83101.99000000001</v>
       </c>
       <c r="F4302" t="n">
-        <v>5189.37640199</v>
+        <v>5185.678888</v>
       </c>
     </row>
     <row r="4303">
@@ -86504,7 +86504,7 @@
         <v>82131.46000000001</v>
       </c>
       <c r="F4304" t="n">
-        <v>7100.55010209</v>
+        <v>7069.16202275</v>
       </c>
     </row>
     <row r="4305">
@@ -86521,10 +86521,70 @@
         <v>80693.69</v>
       </c>
       <c r="E4305" t="n">
-        <v>81666.92</v>
+        <v>81500.03999999999</v>
       </c>
       <c r="F4305" t="n">
-        <v>4980.69655974</v>
+        <v>5106.04567554</v>
+      </c>
+    </row>
+    <row r="4306">
+      <c r="A4306" s="1" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B4306" t="n">
+        <v>81500.03999999999</v>
+      </c>
+      <c r="C4306" t="n">
+        <v>81655.47</v>
+      </c>
+      <c r="D4306" t="n">
+        <v>80700</v>
+      </c>
+      <c r="E4306" t="n">
+        <v>81378.21000000001</v>
+      </c>
+      <c r="F4306" t="n">
+        <v>1892.88624593</v>
+      </c>
+    </row>
+    <row r="4307">
+      <c r="A4307" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B4307" t="n">
+        <v>81387.16</v>
+      </c>
+      <c r="C4307" t="n">
+        <v>82183.56</v>
+      </c>
+      <c r="D4307" t="n">
+        <v>80564.57000000001</v>
+      </c>
+      <c r="E4307" t="n">
+        <v>82006.85000000001</v>
+      </c>
+      <c r="F4307" t="n">
+        <v>2943.48385696</v>
+      </c>
+    </row>
+    <row r="4308">
+      <c r="A4308" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B4308" t="n">
+        <v>82006.85000000001</v>
+      </c>
+      <c r="C4308" t="n">
+        <v>83076.23</v>
+      </c>
+      <c r="D4308" t="n">
+        <v>81634.42999999999</v>
+      </c>
+      <c r="E4308" t="n">
+        <v>82034.56</v>
+      </c>
+      <c r="F4308" t="n">
+        <v>4687.09837202</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4308"/>
+  <dimension ref="A1:F4309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86581,10 +86581,30 @@
         <v>81634.42999999999</v>
       </c>
       <c r="E4308" t="n">
-        <v>82034.56</v>
+        <v>81837.69</v>
       </c>
       <c r="F4308" t="n">
-        <v>4687.09837202</v>
+        <v>4793.78945943</v>
+      </c>
+    </row>
+    <row r="4309">
+      <c r="A4309" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B4309" t="n">
+        <v>81837.7</v>
+      </c>
+      <c r="C4309" t="n">
+        <v>83344.25</v>
+      </c>
+      <c r="D4309" t="n">
+        <v>81080.64</v>
+      </c>
+      <c r="E4309" t="n">
+        <v>83021.61</v>
+      </c>
+      <c r="F4309" t="n">
+        <v>5083.59044303</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4315"/>
+  <dimension ref="A1:F4316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86704,7 +86704,7 @@
         <v>80053.16</v>
       </c>
       <c r="F4314" t="n">
-        <v>2097.00890736</v>
+        <v>2091.79075097</v>
       </c>
     </row>
     <row r="4315">
@@ -86721,10 +86721,30 @@
         <v>79255</v>
       </c>
       <c r="E4315" t="n">
-        <v>79880.82000000001</v>
+        <v>80008.78999999999</v>
       </c>
       <c r="F4315" t="n">
-        <v>6606.83811868</v>
+        <v>6771.4759168</v>
+      </c>
+    </row>
+    <row r="4316">
+      <c r="A4316" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B4316" t="n">
+        <v>80008.78999999999</v>
+      </c>
+      <c r="C4316" t="n">
+        <v>81182</v>
+      </c>
+      <c r="D4316" t="n">
+        <v>79365.92999999999</v>
+      </c>
+      <c r="E4316" t="n">
+        <v>80837.55</v>
+      </c>
+      <c r="F4316" t="n">
+        <v>4262.20970891</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4316"/>
+  <dimension ref="A1:F4317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86724,7 +86724,7 @@
         <v>80008.78999999999</v>
       </c>
       <c r="F4315" t="n">
-        <v>6771.4759168</v>
+        <v>6750.23916109</v>
       </c>
     </row>
     <row r="4316">
@@ -86741,10 +86741,30 @@
         <v>79365.92999999999</v>
       </c>
       <c r="E4316" t="n">
-        <v>80837.55</v>
+        <v>80799.50999999999</v>
       </c>
       <c r="F4316" t="n">
-        <v>4262.20970891</v>
+        <v>4523.14929628</v>
+      </c>
+    </row>
+    <row r="4317">
+      <c r="A4317" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B4317" t="n">
+        <v>80799.5</v>
+      </c>
+      <c r="C4317" t="n">
+        <v>81715.00999999999</v>
+      </c>
+      <c r="D4317" t="n">
+        <v>80270.67999999999</v>
+      </c>
+      <c r="E4317" t="n">
+        <v>81092.38</v>
+      </c>
+      <c r="F4317" t="n">
+        <v>4944.71040304</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4317"/>
+  <dimension ref="A1:F4318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86684,7 +86684,7 @@
         <v>80769.67</v>
       </c>
       <c r="F4313" t="n">
-        <v>3728.91344395</v>
+        <v>3709.57330633</v>
       </c>
     </row>
     <row r="4314">
@@ -86744,7 +86744,7 @@
         <v>80799.50999999999</v>
       </c>
       <c r="F4316" t="n">
-        <v>4523.14929628</v>
+        <v>4520.24579853</v>
       </c>
     </row>
     <row r="4317">
@@ -86761,10 +86761,30 @@
         <v>80270.67999999999</v>
       </c>
       <c r="E4317" t="n">
-        <v>81092.38</v>
+        <v>81249.31</v>
       </c>
       <c r="F4317" t="n">
-        <v>4944.71040304</v>
+        <v>5150.28741801</v>
+      </c>
+    </row>
+    <row r="4318">
+      <c r="A4318" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B4318" t="n">
+        <v>81249.32000000001</v>
+      </c>
+      <c r="C4318" t="n">
+        <v>81890</v>
+      </c>
+      <c r="D4318" t="n">
+        <v>78177.37</v>
+      </c>
+      <c r="E4318" t="n">
+        <v>78962.66</v>
+      </c>
+      <c r="F4318" t="n">
+        <v>8423.27732429</v>
       </c>
     </row>
   </sheetData>

--- a/database/BTCUSD.xlsx
+++ b/database/BTCUSD.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4318"/>
+  <dimension ref="A1:F4319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86744,7 +86744,7 @@
         <v>80799.50999999999</v>
       </c>
       <c r="F4316" t="n">
-        <v>4520.24579853</v>
+        <v>4356.18246596</v>
       </c>
     </row>
     <row r="4317">
@@ -86764,7 +86764,7 @@
         <v>81249.31</v>
       </c>
       <c r="F4317" t="n">
-        <v>5150.28741801</v>
+        <v>5146.98648948</v>
       </c>
     </row>
     <row r="4318">
@@ -86778,13 +86778,33 @@
         <v>81890</v>
       </c>
       <c r="D4318" t="n">
-        <v>78177.37</v>
+        <v>77699</v>
       </c>
       <c r="E4318" t="n">
-        <v>78962.66</v>
+        <v>77780.33</v>
       </c>
       <c r="F4318" t="n">
-        <v>8423.27732429</v>
+        <v>9933.615061529999</v>
+      </c>
+    </row>
+    <row r="4319">
+      <c r="A4319" s="1" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B4319" t="n">
+        <v>77782.75</v>
+      </c>
+      <c r="C4319" t="n">
+        <v>78634.8</v>
+      </c>
+      <c r="D4319" t="n">
+        <v>76141.02</v>
+      </c>
+      <c r="E4319" t="n">
+        <v>76618.57000000001</v>
+      </c>
+      <c r="F4319" t="n">
+        <v>13426.72790301</v>
       </c>
     </row>
   </sheetData>
